--- a/test.xlsx
+++ b/test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paola\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AE7BE0-FA56-41DF-BB37-BF79F3C76072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA42D1E-FCC8-4C2F-84D0-D5188B528BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B00FAA6-D072-47EE-8A13-E06B226FB9D4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="85">
   <si>
     <t>Raccolta, analisi ed uso delle informazioni</t>
   </si>
@@ -280,6 +280,15 @@
   </si>
   <si>
     <t>Premoli Gianluca</t>
+  </si>
+  <si>
+    <t>Di Francesco Roberto</t>
+  </si>
+  <si>
+    <t>Alesii Genuino</t>
+  </si>
+  <si>
+    <t>De cesaro Franco</t>
   </si>
 </sst>
 </file>
@@ -698,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9ED96AD-47F5-4160-A412-F745AC5E508B}">
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -809,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="O2" s="5">
-        <f t="shared" ref="O2:O33" si="0">AVERAGE(C2:N2)</f>
+        <f t="shared" ref="O2:O34" si="0">AVERAGE(C2:N2)</f>
         <v>3.0416666666666665</v>
       </c>
     </row>
@@ -1967,412 +1976,411 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G27" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="H27" s="1">
+        <v>3</v>
+      </c>
+      <c r="I27" s="1">
+        <v>3</v>
+      </c>
+      <c r="J27" s="1">
+        <v>3</v>
+      </c>
+      <c r="K27" s="1">
+        <v>3</v>
+      </c>
+      <c r="L27" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M27" s="1">
+        <v>3</v>
+      </c>
+      <c r="N27" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O27" s="5">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E27" s="1">
-        <v>3</v>
-      </c>
-      <c r="F27" s="1">
-        <v>3</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="C28" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1">
         <v>2</v>
       </c>
-      <c r="H27" s="1">
-        <v>3</v>
-      </c>
-      <c r="I27" s="1">
+      <c r="H28" s="1">
+        <v>3</v>
+      </c>
+      <c r="I28" s="1">
         <v>4</v>
       </c>
-      <c r="J27" s="1">
-        <v>3</v>
-      </c>
-      <c r="K27" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="L27" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M27" s="1">
-        <v>3</v>
-      </c>
-      <c r="N27" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O27" s="5">
+      <c r="J28" s="1">
+        <v>3</v>
+      </c>
+      <c r="K28" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="L28" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M28" s="1">
+        <v>3</v>
+      </c>
+      <c r="N28" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O28" s="5">
         <f t="shared" si="0"/>
         <v>2.9583333333333335</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E28" s="1">
-        <v>3</v>
-      </c>
-      <c r="F28" s="1">
-        <v>3</v>
-      </c>
-      <c r="G28" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H28" s="1">
-        <v>3</v>
-      </c>
-      <c r="I28" s="1">
-        <v>3</v>
-      </c>
-      <c r="J28" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="K28" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="L28" s="1">
+      <c r="C29" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H29" s="1">
+        <v>3</v>
+      </c>
+      <c r="I29" s="1">
+        <v>3</v>
+      </c>
+      <c r="J29" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="K29" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="L29" s="1">
         <v>2</v>
       </c>
-      <c r="M28" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="N28" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O28" s="5">
+      <c r="M29" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="N29" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O29" s="5">
         <f t="shared" si="0"/>
         <v>2.7916666666666665</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="1">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E29" s="1">
-        <v>3</v>
-      </c>
-      <c r="F29" s="1">
-        <v>3</v>
-      </c>
-      <c r="G29" s="1">
-        <v>3</v>
-      </c>
-      <c r="H29" s="1">
-        <v>3</v>
-      </c>
-      <c r="I29" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="J29" s="1">
-        <v>3</v>
-      </c>
-      <c r="K29" s="1">
-        <v>3</v>
-      </c>
-      <c r="L29" s="1">
-        <v>3</v>
-      </c>
-      <c r="M29" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N29" s="1">
-        <v>3</v>
-      </c>
-      <c r="O29" s="5">
+      <c r="C30" s="1">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1">
+        <v>3</v>
+      </c>
+      <c r="G30" s="1">
+        <v>3</v>
+      </c>
+      <c r="H30" s="1">
+        <v>3</v>
+      </c>
+      <c r="I30" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J30" s="1">
+        <v>3</v>
+      </c>
+      <c r="K30" s="1">
+        <v>3</v>
+      </c>
+      <c r="L30" s="1">
+        <v>3</v>
+      </c>
+      <c r="M30" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="N30" s="1">
+        <v>3</v>
+      </c>
+      <c r="O30" s="5">
         <f t="shared" si="0"/>
         <v>2.9583333333333335</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="D30" s="1">
-        <v>3</v>
-      </c>
-      <c r="E30" s="1">
-        <v>3</v>
-      </c>
-      <c r="F30" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="G30" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H30" s="1">
-        <v>3</v>
-      </c>
-      <c r="I30" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="J30" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="K30" s="1">
-        <v>3</v>
-      </c>
-      <c r="L30" s="1">
-        <v>3</v>
-      </c>
-      <c r="M30" s="1">
-        <v>3</v>
-      </c>
-      <c r="N30" s="1">
-        <v>3</v>
-      </c>
-      <c r="O30" s="5">
+      <c r="C31" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3</v>
+      </c>
+      <c r="I31" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J31" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="K31" s="1">
+        <v>3</v>
+      </c>
+      <c r="L31" s="1">
+        <v>3</v>
+      </c>
+      <c r="M31" s="1">
+        <v>3</v>
+      </c>
+      <c r="N31" s="1">
+        <v>3</v>
+      </c>
+      <c r="O31" s="5">
         <f t="shared" si="0"/>
         <v>3.125</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="D31" s="1">
-        <v>3</v>
-      </c>
-      <c r="E31" s="1">
-        <v>3</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="G31" s="1">
-        <v>3</v>
-      </c>
-      <c r="H31" s="1">
-        <v>3</v>
-      </c>
-      <c r="I31" s="1">
-        <v>3</v>
-      </c>
-      <c r="J31" s="1">
-        <v>3</v>
-      </c>
-      <c r="K31" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="L31" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M31" s="1">
-        <v>3</v>
-      </c>
-      <c r="N31" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O31" s="5">
+      <c r="C32" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3</v>
+      </c>
+      <c r="H32" s="1">
+        <v>3</v>
+      </c>
+      <c r="I32" s="1">
+        <v>3</v>
+      </c>
+      <c r="J32" s="1">
+        <v>3</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="L32" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M32" s="1">
+        <v>3</v>
+      </c>
+      <c r="N32" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O32" s="5">
         <f t="shared" si="0"/>
         <v>2.875</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="1">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E32" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="G32" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H32" s="1">
-        <v>3</v>
-      </c>
-      <c r="I32" s="1">
-        <v>3</v>
-      </c>
-      <c r="J32" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="L32" s="1">
-        <v>3</v>
-      </c>
-      <c r="M32" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="N32" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O32" s="5">
+      <c r="C33" s="1">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H33" s="1">
+        <v>3</v>
+      </c>
+      <c r="I33" s="1">
+        <v>3</v>
+      </c>
+      <c r="J33" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="K33" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="L33" s="1">
+        <v>3</v>
+      </c>
+      <c r="M33" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="N33" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O33" s="5">
         <f t="shared" si="0"/>
         <v>2.75</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C34" s="1">
         <v>4</v>
       </c>
-      <c r="D33" s="1">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="F33" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="G33" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H33" s="1">
-        <v>3</v>
-      </c>
-      <c r="I33" s="1">
-        <v>3</v>
-      </c>
-      <c r="J33" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="K33" s="1">
-        <v>3</v>
-      </c>
-      <c r="L33" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M33" s="1">
-        <v>3</v>
-      </c>
-      <c r="N33" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O33" s="5">
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F34" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H34" s="1">
+        <v>3</v>
+      </c>
+      <c r="I34" s="1">
+        <v>3</v>
+      </c>
+      <c r="J34" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="K34" s="1">
+        <v>3</v>
+      </c>
+      <c r="L34" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M34" s="1">
+        <v>3</v>
+      </c>
+      <c r="N34" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O34" s="5">
         <f t="shared" si="0"/>
         <v>3.0833333333333335</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="1">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="E34" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="F34" s="1">
-        <v>3</v>
-      </c>
-      <c r="G34" s="1">
-        <v>3</v>
-      </c>
-      <c r="H34" s="1">
-        <v>3</v>
-      </c>
-      <c r="I34" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="J34" s="1">
-        <v>3</v>
-      </c>
-      <c r="K34" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="L34" s="1">
-        <v>3</v>
-      </c>
-      <c r="M34" s="1">
-        <v>3</v>
-      </c>
-      <c r="N34" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O34" s="5">
-        <f t="shared" ref="O34:O64" si="1">AVERAGE(C34:N34)</f>
-        <v>2.9583333333333335</v>
-      </c>
-    </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E35" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F35" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H35" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I35" s="1">
         <v>3.5</v>
@@ -2381,7 +2389,7 @@
         <v>3</v>
       </c>
       <c r="K35" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L35" s="1">
         <v>3</v>
@@ -2393,301 +2401,301 @@
         <v>2.5</v>
       </c>
       <c r="O35" s="5">
+        <f t="shared" ref="O35:O65" si="1">AVERAGE(C35:N35)</f>
+        <v>2.9583333333333335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I36" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J36" s="1">
+        <v>3</v>
+      </c>
+      <c r="K36" s="1">
+        <v>3</v>
+      </c>
+      <c r="L36" s="1">
+        <v>3</v>
+      </c>
+      <c r="M36" s="1">
+        <v>3</v>
+      </c>
+      <c r="N36" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O36" s="5">
         <f t="shared" si="1"/>
         <v>2.875</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="D36" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E36" s="1">
-        <v>3</v>
-      </c>
-      <c r="F36" s="1">
-        <v>3</v>
-      </c>
-      <c r="G36" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H36" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="I36" s="1">
-        <v>3</v>
-      </c>
-      <c r="J36" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="K36" s="1">
-        <v>3</v>
-      </c>
-      <c r="L36" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M36" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N36" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O36" s="5">
+      <c r="C37" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3</v>
+      </c>
+      <c r="F37" s="1">
+        <v>3</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I37" s="1">
+        <v>3</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="K37" s="1">
+        <v>3</v>
+      </c>
+      <c r="L37" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M37" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="N37" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O37" s="5">
         <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C38" s="1">
         <v>4</v>
       </c>
-      <c r="D37" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="E37" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="F37" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="G37" s="1">
-        <v>3</v>
-      </c>
-      <c r="H37" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="I37" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="J37" s="1">
+      <c r="D38" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F38" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>3</v>
+      </c>
+      <c r="H38" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="I38" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J38" s="1">
         <v>4</v>
       </c>
-      <c r="K37" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="L37" s="1">
-        <v>3</v>
-      </c>
-      <c r="M37" s="1">
+      <c r="K38" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="L38" s="1">
+        <v>3</v>
+      </c>
+      <c r="M38" s="1">
         <v>4</v>
       </c>
-      <c r="N37" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="O37" s="5">
+      <c r="N38" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="O38" s="5">
         <f t="shared" si="1"/>
         <v>3.5416666666666665</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="D38" s="1">
-        <v>3</v>
-      </c>
-      <c r="E38" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="F38" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="G38" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H38" s="1">
-        <v>3</v>
-      </c>
-      <c r="I38" s="1">
-        <v>3</v>
-      </c>
-      <c r="J38" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="K38" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="L38" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M38" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N38" s="1">
-        <v>3</v>
-      </c>
-      <c r="O38" s="5">
+      <c r="C39" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="F39" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H39" s="1">
+        <v>3</v>
+      </c>
+      <c r="I39" s="1">
+        <v>3</v>
+      </c>
+      <c r="J39" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="K39" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="L39" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M39" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="N39" s="1">
+        <v>3</v>
+      </c>
+      <c r="O39" s="5">
         <f t="shared" si="1"/>
         <v>2.9166666666666665</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="D39" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E39" s="1">
-        <v>3</v>
-      </c>
-      <c r="F39" s="1">
-        <v>3</v>
-      </c>
-      <c r="G39" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H39" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="I39" s="1">
-        <v>3</v>
-      </c>
-      <c r="J39" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="K39" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="L39" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M39" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N39" s="1">
-        <v>3</v>
-      </c>
-      <c r="O39" s="5">
+      <c r="C40" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E40" s="1">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1">
+        <v>3</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I40" s="1">
+        <v>3</v>
+      </c>
+      <c r="J40" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="K40" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="L40" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M40" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="1">
+        <v>3</v>
+      </c>
+      <c r="O40" s="5">
         <f t="shared" si="1"/>
         <v>2.8333333333333335</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="1">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E40" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="F40" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="G40" s="1">
-        <v>3</v>
-      </c>
-      <c r="H40" s="1">
-        <v>3</v>
-      </c>
-      <c r="I40" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="J40" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="K40" s="1">
-        <v>3</v>
-      </c>
-      <c r="L40" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M40" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="1">
+      <c r="C41" s="1">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="F41" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G41" s="1">
+        <v>3</v>
+      </c>
+      <c r="H41" s="1">
+        <v>3</v>
+      </c>
+      <c r="I41" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="K41" s="1">
+        <v>3</v>
+      </c>
+      <c r="L41" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M41" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="N41" s="1">
         <v>2</v>
       </c>
-      <c r="O40" s="5">
+      <c r="O41" s="5">
         <f t="shared" si="1"/>
         <v>2.7083333333333335</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="D41" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E41" s="1">
-        <v>2</v>
-      </c>
-      <c r="F41" s="1">
-        <v>2</v>
-      </c>
-      <c r="G41" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H41" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="I41" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="J41" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="K41" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="L41" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M41" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N41" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O41" s="5">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-    </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>16</v>
@@ -2696,31 +2704,31 @@
         <v>2.5</v>
       </c>
       <c r="D42" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E42" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H42" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I42" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J42" s="1">
         <v>2.5</v>
       </c>
       <c r="K42" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L42" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M42" s="1">
         <v>2.5</v>
@@ -2730,21 +2738,21 @@
       </c>
       <c r="O42" s="5">
         <f t="shared" si="1"/>
-        <v>2.875</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D43" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -2753,40 +2761,40 @@
         <v>3</v>
       </c>
       <c r="G43" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H43" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I43" s="1">
         <v>2.5</v>
       </c>
       <c r="J43" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K43" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L43" s="1">
         <v>3</v>
       </c>
-      <c r="M43" s="2">
-        <v>3</v>
-      </c>
-      <c r="N43" s="2">
-        <v>2</v>
+      <c r="M43" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="N43" s="1">
+        <v>2.5</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="1"/>
-        <v>2.75</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1">
         <v>3</v>
@@ -2795,16 +2803,16 @@
         <v>2.5</v>
       </c>
       <c r="E44" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F44" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G44" s="1">
         <v>2.5</v>
       </c>
       <c r="H44" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I44" s="1">
         <v>2.5</v>
@@ -2818,35 +2826,35 @@
       <c r="L44" s="1">
         <v>3</v>
       </c>
-      <c r="M44" s="1">
-        <v>3</v>
-      </c>
-      <c r="N44" s="1">
-        <v>3.5</v>
+      <c r="M44" s="2">
+        <v>3</v>
+      </c>
+      <c r="N44" s="2">
+        <v>2</v>
       </c>
       <c r="O44" s="5">
         <f t="shared" si="1"/>
-        <v>2.9166666666666665</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C45" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D45" s="1">
         <v>2.5</v>
       </c>
       <c r="E45" s="1">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="F45" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G45" s="1">
         <v>2.5</v>
@@ -2855,7 +2863,7 @@
         <v>2.5</v>
       </c>
       <c r="I45" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J45" s="1">
         <v>3</v>
@@ -2866,38 +2874,38 @@
       <c r="L45" s="1">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3">
-        <v>3</v>
+      <c r="M45" s="1">
+        <v>3</v>
+      </c>
+      <c r="N45" s="1">
+        <v>3.5</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="1"/>
-        <v>2.7916666666666665</v>
+        <v>2.9166666666666665</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C46" s="1">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D46" s="1">
         <v>2.5</v>
       </c>
       <c r="E46" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F46" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G46" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H46" s="1">
         <v>2.5</v>
@@ -2906,76 +2914,76 @@
         <v>3.5</v>
       </c>
       <c r="J46" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K46" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L46" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M46" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N46" s="1">
-        <v>2.5</v>
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3">
+        <v>3</v>
       </c>
       <c r="O46" s="5">
         <f t="shared" si="1"/>
-        <v>2.9166666666666665</v>
+        <v>2.7916666666666665</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C47" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E47" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F47" s="1">
         <v>3</v>
       </c>
       <c r="G47" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" s="1">
         <v>2.5</v>
       </c>
       <c r="I47" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J47" s="1">
         <v>3.5</v>
       </c>
       <c r="K47" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L47" s="1">
         <v>2.5</v>
       </c>
       <c r="M47" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N47" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O47" s="5">
         <f t="shared" si="1"/>
-        <v>2.7916666666666665</v>
+        <v>2.9166666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>17</v>
@@ -2990,10 +2998,10 @@
         <v>3.5</v>
       </c>
       <c r="F48" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G48" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="1">
         <v>2.5</v>
@@ -3002,7 +3010,7 @@
         <v>3</v>
       </c>
       <c r="J48" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K48" s="1">
         <v>2.5</v>
@@ -3011,37 +3019,37 @@
         <v>2.5</v>
       </c>
       <c r="M48" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N48" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O48" s="5">
         <f t="shared" si="1"/>
-        <v>2.875</v>
+        <v>2.7916666666666665</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C49" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D49" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E49" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F49" s="1">
         <v>3.5</v>
       </c>
       <c r="G49" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H49" s="1">
         <v>2.5</v>
@@ -3053,64 +3061,64 @@
         <v>3</v>
       </c>
       <c r="K49" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L49" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M49" s="1">
         <v>2.5</v>
       </c>
       <c r="N49" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O49" s="5">
         <f t="shared" si="1"/>
-        <v>2.9166666666666665</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C50" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D50" s="1">
         <v>2.5</v>
       </c>
       <c r="E50" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F50" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G50" s="1">
         <v>2.5</v>
       </c>
       <c r="H50" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I50" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J50" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K50" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L50" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M50" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="N50" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O50" s="5">
         <f t="shared" si="1"/>
@@ -3119,19 +3127,19 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C51" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D51" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E51" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F51" s="1">
         <v>3</v>
@@ -3143,79 +3151,79 @@
         <v>3</v>
       </c>
       <c r="I51" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K51" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L51" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M51" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O51" s="5">
         <f t="shared" si="1"/>
-        <v>2.9583333333333335</v>
+        <v>2.9166666666666665</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C52" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D52" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E52" s="1">
         <v>3</v>
       </c>
       <c r="F52" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G52" s="1">
         <v>2.5</v>
       </c>
       <c r="H52" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I52" s="1">
         <v>3</v>
       </c>
       <c r="J52" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K52" s="1">
         <v>3</v>
       </c>
       <c r="L52" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M52" s="1">
         <v>3</v>
       </c>
       <c r="N52" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O52" s="5">
         <f t="shared" si="1"/>
-        <v>2.875</v>
+        <v>2.9583333333333335</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>18</v>
@@ -3224,28 +3232,28 @@
         <v>3</v>
       </c>
       <c r="D53" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E53" s="1">
         <v>3</v>
       </c>
       <c r="F53" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G53" s="1">
         <v>2.5</v>
       </c>
       <c r="H53" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I53" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J53" s="1">
         <v>3</v>
       </c>
       <c r="K53" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L53" s="1">
         <v>3</v>
@@ -3254,22 +3262,22 @@
         <v>3</v>
       </c>
       <c r="N53" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O53" s="5">
         <f t="shared" si="1"/>
-        <v>2.75</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C54" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D54" s="1">
         <v>2.5</v>
@@ -3278,40 +3286,40 @@
         <v>3</v>
       </c>
       <c r="F54" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G54" s="1">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="H54" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I54" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J54" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K54" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L54" s="1">
         <v>3</v>
       </c>
       <c r="M54" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N54" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O54" s="5">
         <f t="shared" si="1"/>
-        <v>3.0833333333333335</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>18</v>
@@ -3320,46 +3328,46 @@
         <v>3.5</v>
       </c>
       <c r="D55" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E55" s="1">
         <v>3</v>
       </c>
       <c r="F55" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G55" s="1">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="H55" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I55" s="1">
         <v>3</v>
       </c>
       <c r="J55" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K55" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L55" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M55" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N55" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O55" s="5">
         <f t="shared" si="1"/>
-        <v>2.75</v>
+        <v>3.0833333333333335</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>18</v>
@@ -3407,115 +3415,115 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="D57" s="4">
-        <v>3</v>
-      </c>
-      <c r="E57" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="F57" s="4">
-        <v>3</v>
-      </c>
-      <c r="G57" s="4">
-        <v>3</v>
-      </c>
-      <c r="H57" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="I57" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="J57" s="4">
+      <c r="C57" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1">
+        <v>3</v>
+      </c>
+      <c r="F57" s="1">
+        <v>3</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I57" s="1">
+        <v>3</v>
+      </c>
+      <c r="J57" s="1">
+        <v>3</v>
+      </c>
+      <c r="K57" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="L57" s="1">
         <v>2</v>
       </c>
-      <c r="K57" s="4">
+      <c r="M57" s="1">
+        <v>3</v>
+      </c>
+      <c r="N57" s="1">
         <v>2</v>
-      </c>
-      <c r="L57" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="M57" s="4">
-        <v>3</v>
-      </c>
-      <c r="N57" s="4">
-        <v>2.5</v>
       </c>
       <c r="O57" s="5">
         <f t="shared" si="1"/>
-        <v>2.6666666666666665</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="1">
-        <v>4</v>
-      </c>
-      <c r="D58" s="1">
-        <v>3</v>
-      </c>
-      <c r="E58" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="F58" s="1">
-        <v>3</v>
-      </c>
-      <c r="G58" s="1">
-        <v>3</v>
-      </c>
-      <c r="H58" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="I58" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="J58" s="1">
-        <v>3</v>
-      </c>
-      <c r="K58" s="1">
+      <c r="C58" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="D58" s="4">
+        <v>3</v>
+      </c>
+      <c r="E58" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="F58" s="4">
+        <v>3</v>
+      </c>
+      <c r="G58" s="4">
+        <v>3</v>
+      </c>
+      <c r="H58" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I58" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="J58" s="4">
         <v>2</v>
       </c>
-      <c r="L58" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M58" s="1">
-        <v>3</v>
-      </c>
-      <c r="N58" s="1">
+      <c r="K58" s="4">
+        <v>2</v>
+      </c>
+      <c r="L58" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="M58" s="4">
+        <v>3</v>
+      </c>
+      <c r="N58" s="4">
         <v>2.5</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="1"/>
-        <v>3.0416666666666665</v>
+        <v>2.6666666666666665</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C59" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" s="1">
         <v>3</v>
       </c>
       <c r="E59" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F59" s="1">
         <v>3</v>
@@ -3524,16 +3532,16 @@
         <v>3</v>
       </c>
       <c r="H59" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I59" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J59" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K59" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L59" s="1">
         <v>2.5</v>
@@ -3546,108 +3554,108 @@
       </c>
       <c r="O59" s="5">
         <f t="shared" si="1"/>
-        <v>2.875</v>
+        <v>3.0416666666666665</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="4">
-        <v>3</v>
-      </c>
-      <c r="D60" s="4">
-        <v>3</v>
-      </c>
-      <c r="E60" s="4">
-        <v>3</v>
-      </c>
-      <c r="F60" s="4">
-        <v>3</v>
-      </c>
-      <c r="G60" s="4">
-        <v>2</v>
-      </c>
-      <c r="H60" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="I60" s="4">
-        <v>3</v>
-      </c>
-      <c r="J60" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="K60" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="L60" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="M60" s="4">
-        <v>3</v>
-      </c>
-      <c r="N60" s="4">
-        <v>2</v>
+      <c r="C60" s="1">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="F60" s="1">
+        <v>3</v>
+      </c>
+      <c r="G60" s="1">
+        <v>3</v>
+      </c>
+      <c r="H60" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I60" s="1">
+        <v>3</v>
+      </c>
+      <c r="J60" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="K60" s="1">
+        <v>3</v>
+      </c>
+      <c r="L60" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M60" s="1">
+        <v>3</v>
+      </c>
+      <c r="N60" s="1">
+        <v>2.5</v>
       </c>
       <c r="O60" s="5">
         <f t="shared" si="1"/>
-        <v>2.6666666666666665</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="1">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1">
-        <v>3</v>
-      </c>
-      <c r="E61" s="1">
-        <v>3</v>
-      </c>
-      <c r="F61" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="G61" s="1">
-        <v>3</v>
-      </c>
-      <c r="H61" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="I61" s="1">
-        <v>3</v>
-      </c>
-      <c r="J61" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="K61" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="L61" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="M61" s="1">
-        <v>3</v>
-      </c>
-      <c r="N61" s="1">
-        <v>3.5</v>
+      <c r="C61" s="4">
+        <v>3</v>
+      </c>
+      <c r="D61" s="4">
+        <v>3</v>
+      </c>
+      <c r="E61" s="4">
+        <v>3</v>
+      </c>
+      <c r="F61" s="4">
+        <v>3</v>
+      </c>
+      <c r="G61" s="4">
+        <v>2</v>
+      </c>
+      <c r="H61" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I61" s="4">
+        <v>3</v>
+      </c>
+      <c r="J61" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="K61" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="L61" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="M61" s="4">
+        <v>3</v>
+      </c>
+      <c r="N61" s="4">
+        <v>2</v>
       </c>
       <c r="O61" s="5">
         <f t="shared" si="1"/>
-        <v>2.9166666666666665</v>
+        <v>2.6666666666666665</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>18</v>
@@ -3659,76 +3667,76 @@
         <v>3</v>
       </c>
       <c r="E62" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F62" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G62" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H62" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I62" s="1">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J62" s="1">
         <v>2.5</v>
       </c>
       <c r="K62" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L62" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M62" s="1">
         <v>3</v>
       </c>
       <c r="N62" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="O62" s="5">
         <f t="shared" si="1"/>
-        <v>2.75</v>
+        <v>2.9166666666666665</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C63" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" s="1">
         <v>3</v>
       </c>
       <c r="E63" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F63" s="1">
         <v>3</v>
       </c>
       <c r="G63" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H63" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I63" s="1">
         <v>3.5</v>
       </c>
       <c r="J63" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K63" s="1">
         <v>2</v>
       </c>
       <c r="L63" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M63" s="1">
         <v>3</v>
@@ -3738,59 +3746,198 @@
       </c>
       <c r="O63" s="5">
         <f t="shared" si="1"/>
-        <v>3.0416666666666665</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" s="1">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F64" s="1">
+        <v>3</v>
+      </c>
+      <c r="G64" s="1">
+        <v>3</v>
+      </c>
+      <c r="H64" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="I64" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J64" s="1">
+        <v>3</v>
+      </c>
+      <c r="K64" s="1">
         <v>2</v>
       </c>
-      <c r="E64" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="F64" s="1">
-        <v>3</v>
-      </c>
-      <c r="G64" s="1">
-        <v>3</v>
-      </c>
-      <c r="H64" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="I64" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="J64" s="1">
-        <v>3</v>
-      </c>
-      <c r="K64" s="1">
-        <v>2.5</v>
-      </c>
       <c r="L64" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M64" s="1">
         <v>3</v>
       </c>
       <c r="N64" s="1">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="O64" s="5">
         <f t="shared" si="1"/>
+        <v>3.0416666666666665</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="1">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="F65" s="1">
+        <v>3</v>
+      </c>
+      <c r="G65" s="1">
+        <v>3</v>
+      </c>
+      <c r="H65" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I65" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="J65" s="1">
+        <v>3</v>
+      </c>
+      <c r="K65" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="L65" s="1">
+        <v>3</v>
+      </c>
+      <c r="M65" s="1">
+        <v>3</v>
+      </c>
+      <c r="N65" s="1">
+        <v>4</v>
+      </c>
+      <c r="O65" s="5">
+        <f t="shared" si="1"/>
         <v>2.8333333333333335</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="1">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3</v>
+      </c>
+      <c r="E66" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F66" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G66" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="H66" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="I66" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J66" s="1">
+        <v>3</v>
+      </c>
+      <c r="K66" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="L66" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M66" s="1">
+        <v>3</v>
+      </c>
+      <c r="N66" s="1">
+        <v>3</v>
+      </c>
+      <c r="O66" s="5">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="D67" s="1">
+        <v>3</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+      <c r="F67" s="1">
+        <v>3</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H67" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I67" s="1">
+        <v>4</v>
+      </c>
+      <c r="J67" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="K67" s="1">
+        <v>3</v>
+      </c>
+      <c r="L67" s="1">
+        <v>3</v>
+      </c>
+      <c r="M67" s="1">
+        <v>3</v>
+      </c>
+      <c r="N67" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O67" s="5">
+        <v>2.79</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
